--- a/data/reports/2024-11-11/2024-11-11_duplicates.xlsx
+++ b/data/reports/2024-11-11/2024-11-11_duplicates.xlsx
@@ -185,7 +185,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004139</t>
+    <t>RMD0009352</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -201,28 +201,28 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>800-7096314</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004139</t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
     <t>800-709-6314</t>
   </si>
   <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009352</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>800-7096314</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008972</t>
@@ -261,7 +261,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009084</t>
+    <t>RMD0009205</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,12 +318,6 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
-  </si>
-  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -346,7 +340,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008869</t>
+    <t>RMD0009084</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -409,7 +409,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004724</t>
+    <t>RMD0005819</t>
   </si>
   <si>
     <t>Ton80 Communications, LLC</t>
@@ -419,16 +419,16 @@
 Anderson SC 29642</t>
   </si>
   <si>
+    <t>4109121000</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004724</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005819</t>
-  </si>
-  <si>
-    <t>4109121000</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004849</t>
@@ -493,10 +493,37 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003758</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach Florida 33139</t>
+  </si>
+  <si>
+    <t>Davon Person</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Network Operations Center</t>
+  </si>
+  <si>
+    <t>1250 E Hallandale Beach Blvd
+Hallandale FL 33009</t>
+  </si>
+  <si>
+    <t>9546248162</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -528,33 +555,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach Florida 33139</t>
-  </si>
-  <si>
-    <t>Davon Person</t>
-  </si>
-  <si>
-    <t>Director of Operations</t>
-  </si>
-  <si>
-    <t>Network Operations Center</t>
-  </si>
-  <si>
-    <t>1250 E Hallandale Beach Blvd
-Hallandale FL 33009</t>
-  </si>
-  <si>
-    <t>9546248162</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005139</t>
@@ -711,7 +711,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -721,6 +721,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -739,13 +745,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005569</t>
+    <t>RMD0005461</t>
   </si>
   <si>
     <t>Valstarr Asia</t>
@@ -755,25 +755,10 @@
 Valley Center CA 92082</t>
   </si>
   <si>
+    <t>0031217672</t>
+  </si>
+  <si>
     <t>Vincent W. Kahn</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Systems Admin</t>
-  </si>
-  <si>
-    <t>'+13213288217</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005461</t>
-  </si>
-  <si>
-    <t>0031217672</t>
   </si>
   <si>
     <t>MANAGER</t>
@@ -793,7 +778,22 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
+    <t>RMD0005569</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Systems Admin</t>
+  </si>
+  <si>
+    <t>'+13213288217</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -806,25 +806,25 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Syed Omar Farooq Shah</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>'+61406851546</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005297</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
-  </si>
-  <si>
-    <t>Syed Omar Farooq Shah</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+61406851546</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
+    <t>RMD0005585</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -838,6 +838,28 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
+  </si>
+  <si>
+    <t>Paul Joncas</t>
+  </si>
+  <si>
+    <t>Operatopms</t>
+  </si>
+  <si>
+    <t>187 Plymouth Avenue
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005574</t>
+  </si>
+  <si>
     <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
   </si>
   <si>
@@ -845,29 +867,20 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005585</t>
-  </si>
-  <si>
-    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
-  </si>
-  <si>
-    <t>Paul Joncas</t>
-  </si>
-  <si>
-    <t>Operatopms</t>
-  </si>
-  <si>
-    <t>187 Plymouth Avenue
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+    <t>RMD0006284</t>
+  </si>
+  <si>
+    <t>Office No 17 3rd Floor Anique Arcade Plaza I8 Markaz
+  Islamabad, Pakistan</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -877,9 +890,6 @@
 federal 46000 Islamabad, Pakistan</t>
   </si>
   <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
     <t>Umair Hassan</t>
   </si>
   <si>
@@ -890,16 +900,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8037e23e1b32781093d3a820f54bcb1c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006284</t>
-  </si>
-  <si>
-    <t>Office No 17 3rd Floor Anique Arcade Plaza I8 Markaz
-  Islamabad, Pakistan</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008125</t>
@@ -931,7 +931,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007626</t>
+    <t>RMD0007575</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -944,16 +944,16 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007626</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007575</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007716</t>
+    <t>RMD0007696</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -963,16 +963,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007716</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -982,6 +982,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -997,13 +1003,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008423</t>
+    <t>RMD0008393</t>
   </si>
   <si>
     <t>Your Business I.T. Inc.</t>
@@ -1011,6 +1011,12 @@
   <si>
     <t>295 Weber St. N
 Ontario N2J 3H8 Waterloo, Canada</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T.</t>
@@ -1028,13 +1034,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=761bc9e71b3eb810d39dddb6bc4bcbe0&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008393</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1044,12 +1044,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1057,7 +1051,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008610</t>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008612</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1067,43 +1067,49 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008611</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
+    <t>Nobe</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008610</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008611</t>
-  </si>
-  <si>
-    <t>Nobe</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008759</t>
+    <t>RMD0008756</t>
   </si>
   <si>
     <t>573 Ocean Blvd
 Hampton NH 03842</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008759</t>
+  </si>
+  <si>
     <t>Jeffrey D Houston</t>
   </si>
   <si>
@@ -1116,13 +1122,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008756</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008755</t>
+    <t>RMD0008798</t>
   </si>
   <si>
     <t>Aspire Holdings Group LLC</t>
@@ -1135,30 +1135,30 @@
     <t>AspirePBX</t>
   </si>
   <si>
+    <t>CP Short</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>6023888700</t>
+  </si>
+  <si>
+    <t>725</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008755</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=82b1054a1b0f30508d57ecace54bcbda&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008798</t>
-  </si>
-  <si>
-    <t>CP Short</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
-    <t>Partner</t>
-  </si>
-  <si>
-    <t>6023888700</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0008787</t>
   </si>
   <si>
@@ -1186,7 +1186,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=29f1aec61b0f3050003c43f1f54bcba5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009161</t>
+    <t>RMD0009160</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1196,16 +1196,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009161</t>
+  </si>
+  <si>
     <t>9497014500</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009160</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -6289,9 +6289,15 @@
       <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J7" s="1" t="s">
         <v>58</v>
       </c>
@@ -6349,15 +6355,9 @@
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
         <v>58</v>
       </c>
@@ -6532,9 +6532,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>34</v>
@@ -6545,14 +6547,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6579,7 +6583,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6588,13 +6592,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>34</v>
@@ -6605,9 +6607,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6626,41 +6626,55 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+      <c r="J13" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
+      <c r="Q13" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R13" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6672,46 +6686,32 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>102</v>
-      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q14" s="1"/>
       <c r="R14" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6737,54 +6737,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6801,33 +6787,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -6946,16 +6946,28 @@
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="M19" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
+        <v>127</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="Q19" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R19" s="1" t="s">
         <v>26</v>
       </c>
@@ -6963,16 +6975,16 @@
         <v>26</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U19" s="1"/>
       <c r="V19" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="1">
         <v>25462672</v>
@@ -6992,28 +7004,16 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>130</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
       <c r="P20" s="1"/>
-      <c r="Q20" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1" t="s">
         <v>26</v>
       </c>
@@ -7021,7 +7021,7 @@
         <v>26</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
@@ -7266,31 +7266,27 @@
       <c r="O25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B26" s="1">
         <v>27710730</v>
@@ -7299,7 +7295,7 @@
         <v>152</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>26</v>
@@ -7311,37 +7307,41 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="N26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U26" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U26" s="1"/>
       <c r="V26" s="1" t="s">
         <v>169</v>
       </c>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R30" s="1" t="s">
         <v>34</v>
@@ -7614,7 +7614,7 @@
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>34</v>
@@ -7805,48 +7805,34 @@
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>222</v>
-      </c>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>223</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q35" s="1"/>
       <c r="R35" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B36" s="1">
         <v>31124688</v>
@@ -7865,25 +7851,39 @@
       </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
+      <c r="I36" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="M36" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+        <v>218</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>225</v>
+      </c>
       <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
+      <c r="Q36" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R36" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1" t="s">
@@ -7909,48 +7909,54 @@
       <c r="F37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
+      <c r="G37" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J37" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B38" s="1">
         <v>31217029</v>
@@ -7967,26 +7973,20 @@
       <c r="F38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
       <c r="J38" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>27</v>
@@ -7996,16 +7996,16 @@
       </c>
       <c r="P38" s="1"/>
       <c r="Q38" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8034,33 +8034,45 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="J39" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="M39" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
+        <v>244</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>248</v>
+      </c>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
+      <c r="Q39" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R39" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B40" s="1">
         <v>31294614</v>
@@ -8080,36 +8092,24 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>189</v>
-      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>250</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q40" s="1"/>
       <c r="R40" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U40" s="1"/>
       <c r="V40" s="1" t="s">
@@ -8141,42 +8141,48 @@
       <c r="H41" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>258</v>
+      </c>
       <c r="M41" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U41" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V41" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B42" s="1">
         <v>31356652</v>
@@ -8197,18 +8203,14 @@
         <v>255</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L42" s="1" t="s">
         <v>263</v>
       </c>
+      <c r="I42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
       <c r="M42" s="1" t="s">
         <v>264</v>
       </c>
@@ -8216,24 +8218,22 @@
         <v>27</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
         <v>265</v>
       </c>
@@ -8255,55 +8255,49 @@
       <c r="F43" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>270</v>
-      </c>
+      <c r="G43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
       <c r="M43" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>271</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q43" s="1"/>
       <c r="R43" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B44" s="1">
         <v>31392434</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>34</v>
@@ -8311,33 +8305,39 @@
       <c r="F44" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="M44" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
+        <v>271</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>274</v>
+      </c>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="Q44" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8385,7 +8385,7 @@
         <v>281</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>33</v>
@@ -8475,9 +8475,7 @@
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
-      <c r="M47" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -8521,7 +8519,9 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
+      <c r="M48" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
@@ -8559,15 +8559,9 @@
       <c r="F49" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -8611,9 +8605,15 @@
       <c r="F50" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
+      <c r="G50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -8652,55 +8652,41 @@
         <v>300</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
       <c r="R51" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U51" s="1"/>
       <c r="V51" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B52" s="1">
         <v>31445216</v>
@@ -8712,32 +8698,46 @@
         <v>300</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
+      <c r="J52" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M52" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
+        <v>300</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R52" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U52" s="1"/>
       <c r="V52" s="1" t="s">
@@ -8766,43 +8766,33 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>313</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
       <c r="P53" s="1"/>
-      <c r="Q53" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B54" s="1">
         <v>31455868</v>
@@ -8822,24 +8812,34 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
+        <v>314</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>315</v>
+      </c>
       <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+      <c r="Q54" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8872,7 +8872,7 @@
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
-        <v>40</v>
+        <v>320</v>
       </c>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -8889,12 +8889,12 @@
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B56" s="1">
         <v>31457815</v>
@@ -8918,7 +8918,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1" t="s">
-        <v>322</v>
+        <v>40</v>
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -8960,33 +8960,45 @@
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
+      <c r="J57" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M57" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
+        <v>326</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>329</v>
+      </c>
       <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
+      <c r="Q57" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R57" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B58" s="1">
         <v>31475270</v>
@@ -9001,50 +9013,40 @@
         <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="I58" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>332</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
       <c r="P58" s="1"/>
-      <c r="Q58" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="Q58" s="1"/>
       <c r="R58" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" spans="1:22">
       <c r="A59" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B59" s="1">
         <v>31475270</v>
@@ -9059,13 +9061,11 @@
         <v>34</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G59" s="1"/>
       <c r="H59" s="1"/>
-      <c r="I59" s="1" t="s">
-        <v>335</v>
-      </c>
+      <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -9102,53 +9102,41 @@
         <v>338</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>280</v>
-      </c>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
       <c r="R60" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B61" s="1">
         <v>31485048</v>
@@ -9158,32 +9146,44 @@
         <v>338</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+      <c r="J61" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>280</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
+        <v>338</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R61" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9204,43 +9204,57 @@
         <v>347</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1" t="s">
         <v>348</v>
       </c>
       <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="J62" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="M62" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
+        <v>347</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="R62" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U62" s="1"/>
       <c r="V62" s="1" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:22">
       <c r="A63" s="1" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B63" s="1">
         <v>31489362</v>
@@ -9252,48 +9266,34 @@
         <v>347</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1" t="s">
         <v>348</v>
       </c>
       <c r="I63" s="1"/>
-      <c r="J63" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>353</v>
-      </c>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>53</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
+      <c r="P63" s="1"/>
+      <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U63" s="1"/>
       <c r="V63" s="1" t="s">
@@ -9343,7 +9343,7 @@
         <v>362</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q64" s="1" t="s">
         <v>33</v>
@@ -9424,49 +9424,39 @@
         <v>368</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="1" t="s">
-        <v>367</v>
-      </c>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
-      <c r="M66" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>369</v>
-      </c>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1"/>
+      <c r="O66" s="1"/>
       <c r="P66" s="1"/>
-      <c r="Q66" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="Q66" s="1"/>
       <c r="R66" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="67" spans="1:22">
       <c r="A67" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B67" s="1">
         <v>31544182</v>
@@ -9478,30 +9468,40 @@
         <v>368</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
+      <c r="J67" s="1" t="s">
+        <v>367</v>
+      </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
+      <c r="M67" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
+      <c r="Q67" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R67" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
@@ -9578,7 +9578,7 @@
         <v>379</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>380</v>
@@ -9594,7 +9594,7 @@
       </c>
       <c r="P69" s="1"/>
       <c r="Q69" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R69" s="1" t="s">
         <v>34</v>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>34</v>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>34</v>
@@ -10056,7 +10056,7 @@
         <v>431</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>189</v>
@@ -10114,7 +10114,7 @@
         <v>437</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>189</v>
@@ -10160,13 +10160,13 @@
         <v>27</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>440</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
@@ -10214,10 +10214,10 @@
         <v>444</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M81" s="1"/>
       <c r="N81" s="1" t="s">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="P82" s="1"/>
       <c r="Q82" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R82" s="1" t="s">
         <v>34</v>
@@ -10340,7 +10340,7 @@
         <v>460</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>461</v>
@@ -10439,7 +10439,7 @@
         <v>34</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
@@ -10457,14 +10457,14 @@
         <v>474</v>
       </c>
       <c r="N85" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O85" s="1" t="s">
         <v>475</v>
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>34</v>
@@ -10566,7 +10566,7 @@
         <v>488</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L87" s="1" t="s">
         <v>489</v>
@@ -10678,7 +10678,7 @@
         <v>500</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>501</v>
@@ -10728,13 +10728,13 @@
         <v>27</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>506</v>
@@ -10796,10 +10796,10 @@
         <v>513</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>512</v>
@@ -11032,7 +11032,7 @@
         <v>540</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L95" s="1"/>
       <c r="M95" s="1" t="s">
@@ -11089,7 +11089,7 @@
         <v>546</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M96" s="1"/>
       <c r="N96" s="1" t="s">
@@ -11144,7 +11144,7 @@
         <v>553</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L97" s="1"/>
       <c r="M97" s="1" t="s">
@@ -11198,7 +11198,7 @@
         <v>559</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>560</v>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="P98" s="1"/>
       <c r="Q98" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R98" s="1" t="s">
         <v>34</v>
@@ -11262,10 +11262,10 @@
         <v>567</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M99" s="1" t="s">
         <v>565</v>
@@ -11278,7 +11278,7 @@
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>34</v>
@@ -11382,7 +11382,7 @@
         <v>581</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>31</v>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>34</v>
@@ -11494,10 +11494,10 @@
         <v>593</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M103" s="1" t="s">
         <v>591</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="P103" s="1"/>
       <c r="Q103" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>34</v>
@@ -11610,7 +11610,7 @@
         <v>605</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="L105" s="1" t="s">
         <v>31</v>
@@ -11718,7 +11718,7 @@
         <v>615</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L107" s="1" t="s">
         <v>616</v>
@@ -11822,10 +11822,10 @@
         <v>625</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>624</v>
@@ -11886,7 +11886,7 @@
         <v>633</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L110" s="1" t="s">
         <v>634</v>
@@ -11997,7 +11997,7 @@
         <v>648</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>644</v>
@@ -12052,10 +12052,10 @@
         <v>654</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>652</v>
@@ -12162,7 +12162,7 @@
         <v>664</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>665</v>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="P115" s="1"/>
       <c r="Q115" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R115" s="1" t="s">
         <v>34</v>
@@ -12214,10 +12214,10 @@
         <v>669</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M116" s="1" t="s">
         <v>670</v>
@@ -12288,7 +12288,7 @@
       </c>
       <c r="P117" s="1"/>
       <c r="Q117" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R117" s="1" t="s">
         <v>34</v>
@@ -12419,7 +12419,7 @@
         <v>34</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>28</v>
@@ -12443,7 +12443,7 @@
         <v>689</v>
       </c>
       <c r="N120" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O120" s="1" t="s">
         <v>693</v>
@@ -12496,7 +12496,7 @@
         <v>698</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L121" s="1" t="s">
         <v>380</v>
@@ -12554,10 +12554,10 @@
         <v>703</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M122" s="1" t="s">
         <v>704</v>
@@ -12570,7 +12570,7 @@
       </c>
       <c r="P122" s="1"/>
       <c r="Q122" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R122" s="1" t="s">
         <v>34</v>
@@ -12599,7 +12599,7 @@
         <v>34</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>28</v>
@@ -12704,10 +12704,10 @@
         <v>714</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M125" s="1"/>
       <c r="N125" s="1" t="s">
@@ -12747,7 +12747,7 @@
         <v>34</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G126" s="1"/>
       <c r="H126" s="1"/>
@@ -12787,7 +12787,7 @@
         <v>34</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -12893,7 +12893,7 @@
         <v>59</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M129" s="1" t="s">
         <v>730</v>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>34</v>
@@ -12949,7 +12949,7 @@
         <v>737</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>734</v>
@@ -13004,10 +13004,10 @@
         <v>743</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M131" s="1"/>
       <c r="N131" s="1" t="s">
@@ -13272,7 +13272,7 @@
         <v>772</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>773</v>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R136" s="1" t="s">
         <v>34</v>
@@ -13330,10 +13330,10 @@
         <v>779</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>777</v>
@@ -13446,7 +13446,7 @@
         <v>791</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>792</v>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="P139" s="1"/>
       <c r="Q139" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R139" s="1" t="s">
         <v>34</v>
@@ -13500,7 +13500,7 @@
         <v>797</v>
       </c>
       <c r="K140" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L140" s="1" t="s">
         <v>798</v>
@@ -13559,7 +13559,7 @@
         <v>59</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>803</v>
@@ -13618,7 +13618,7 @@
         <v>810</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L142" s="1"/>
       <c r="M142" s="1" t="s">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R142" s="1" t="s">
         <v>26</v>
@@ -13678,10 +13678,10 @@
         <v>815</v>
       </c>
       <c r="K143" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>816</v>
@@ -13785,7 +13785,7 @@
         <v>34</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -13803,14 +13803,14 @@
         <v>829</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O145" s="1" t="s">
         <v>830</v>
       </c>
       <c r="P145" s="1"/>
       <c r="Q145" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R145" s="1" t="s">
         <v>34</v>
@@ -13948,10 +13948,10 @@
         <v>844</v>
       </c>
       <c r="K148" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M148" s="1" t="s">
         <v>843</v>
@@ -14020,7 +14020,7 @@
       </c>
       <c r="P149" s="1"/>
       <c r="Q149" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R149" s="1" t="s">
         <v>34</v>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="P150" s="1"/>
       <c r="Q150" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R150" s="1" t="s">
         <v>26</v>
@@ -14188,7 +14188,7 @@
       </c>
       <c r="P152" s="1"/>
       <c r="Q152" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R152" s="1" t="s">
         <v>34</v>
@@ -14272,14 +14272,14 @@
         <v>27</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>877</v>
       </c>
       <c r="I154" s="1"/>
       <c r="J154" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K154" s="1" t="s">
         <v>59</v>
@@ -14382,7 +14382,7 @@
         <v>886</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L156" s="1" t="s">
         <v>507</v>
@@ -14444,7 +14444,7 @@
         <v>893</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="L157" s="1" t="s">
         <v>894</v>
@@ -14507,7 +14507,7 @@
         <v>467</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M158" s="1"/>
       <c r="N158" s="1" t="s">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="P158" s="1"/>
       <c r="Q158" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R158" s="1" t="s">
         <v>34</v>
@@ -14564,7 +14564,7 @@
         <v>907</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>189</v>
@@ -14623,7 +14623,7 @@
         <v>913</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M160" s="1"/>
       <c r="N160" s="1" t="s">
@@ -14676,7 +14676,7 @@
         <v>919</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L161" s="1" t="s">
         <v>920</v>
@@ -14736,10 +14736,10 @@
         <v>928</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>929</v>
@@ -14752,7 +14752,7 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>34</v>
@@ -14786,13 +14786,13 @@
         <v>27</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H163" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J163" s="1" t="s">
         <v>934</v>
@@ -14801,7 +14801,7 @@
         <v>59</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M163" s="1" t="s">
         <v>933</v>
@@ -14814,7 +14814,7 @@
       </c>
       <c r="P163" s="1"/>
       <c r="Q163" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R163" s="1" t="s">
         <v>34</v>
@@ -14952,7 +14952,7 @@
         <v>27</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H166" s="1"/>
       <c r="I166" s="1"/>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="P167" s="1"/>
       <c r="Q167" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R167" s="1" t="s">
         <v>26</v>
@@ -15095,7 +15095,7 @@
         <v>34</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>28</v>
@@ -15119,7 +15119,7 @@
         <v>965</v>
       </c>
       <c r="N169" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O169" s="1" t="s">
         <v>966</v>
@@ -15160,7 +15160,7 @@
         <v>27</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>970</v>
@@ -15302,7 +15302,7 @@
         <v>986</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>26</v>
@@ -15483,7 +15483,7 @@
         <v>34</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
@@ -15492,14 +15492,14 @@
         <v>1003</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L176" s="1" t="s">
         <v>189</v>
       </c>
       <c r="M176" s="1"/>
       <c r="N176" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="O176" s="1" t="s">
         <v>1004</v>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="P178" s="1"/>
       <c r="Q178" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R178" s="1" t="s">
         <v>34</v>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="P180" s="1"/>
       <c r="Q180" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R180" s="1" t="s">
         <v>34</v>
@@ -15965,7 +15965,7 @@
         <v>1053</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M185" s="1" t="s">
         <v>1054</v>
@@ -16135,7 +16135,7 @@
         <v>1072</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M188" s="1" t="s">
         <v>1073</v>
@@ -16195,7 +16195,7 @@
         <v>1080</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M189" s="1" t="s">
         <v>1077</v>
@@ -16255,7 +16255,7 @@
         <v>59</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M190" s="1" t="s">
         <v>1084</v>
@@ -16350,13 +16350,13 @@
         <v>27</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>1097</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J192" s="1" t="s">
         <v>1098</v>
@@ -16365,7 +16365,7 @@
         <v>1099</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M192" s="1" t="s">
         <v>1096</v>
@@ -16422,7 +16422,7 @@
         <v>1105</v>
       </c>
       <c r="K193" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L193" s="1" t="s">
         <v>1106</v>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="P193" s="1"/>
       <c r="Q193" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R193" s="1" t="s">
         <v>34</v>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="P195" s="1"/>
       <c r="Q195" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R195" s="1" t="s">
         <v>34</v>
@@ -16599,7 +16599,7 @@
         <v>59</v>
       </c>
       <c r="L196" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M196" s="1"/>
       <c r="N196" s="1" t="s">
@@ -16768,13 +16768,13 @@
         <v>27</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H199" s="1" t="s">
         <v>1144</v>
       </c>
       <c r="I199" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J199" s="1"/>
       <c r="K199" s="1"/>
@@ -16830,10 +16830,10 @@
         <v>1149</v>
       </c>
       <c r="K200" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>1147</v>
@@ -17066,7 +17066,7 @@
       </c>
       <c r="P204" s="1"/>
       <c r="Q204" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>34</v>
@@ -17108,10 +17108,10 @@
         <v>1182</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M205" s="1" t="s">
         <v>1180</v>
@@ -17124,7 +17124,7 @@
       </c>
       <c r="P205" s="1"/>
       <c r="Q205" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R205" s="1" t="s">
         <v>26</v>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="P206" s="1"/>
       <c r="Q206" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R206" s="1" t="s">
         <v>34</v>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="P207" s="1"/>
       <c r="Q207" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R207" s="1" t="s">
         <v>34</v>
@@ -17346,13 +17346,13 @@
         <v>185</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I209" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J209" s="1" t="s">
         <v>1208</v>
@@ -17482,10 +17482,10 @@
         <v>1226</v>
       </c>
       <c r="K211" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M211" s="1" t="s">
         <v>1227</v>
@@ -17560,7 +17560,7 @@
       </c>
       <c r="P212" s="1"/>
       <c r="Q212" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R212" s="1" t="s">
         <v>34</v>
@@ -17620,7 +17620,7 @@
       </c>
       <c r="P213" s="1"/>
       <c r="Q213" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R213" s="1" t="s">
         <v>34</v>
@@ -17656,7 +17656,7 @@
         <v>891</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
@@ -17770,7 +17770,7 @@
         <v>1251</v>
       </c>
       <c r="K216" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L216" s="1" t="s">
         <v>189</v>
@@ -17893,7 +17893,7 @@
         <v>1264</v>
       </c>
       <c r="L218" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M218" s="1" t="s">
         <v>1265</v>
@@ -17957,7 +17957,7 @@
         <v>1271</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M219" s="1" t="s">
         <v>1272</v>
@@ -18017,7 +18017,7 @@
         <v>1281</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M220" s="1" t="s">
         <v>1278</v>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="P221" s="1"/>
       <c r="Q221" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R221" s="1" t="s">
         <v>26</v>
@@ -18448,10 +18448,10 @@
         <v>1329</v>
       </c>
       <c r="K227" s="1" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M227" s="1" t="s">
         <v>1330</v>
@@ -18502,13 +18502,13 @@
         <v>27</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>1336</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J228" s="1" t="s">
         <v>1337</v>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>34</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R231" s="1" t="s">
         <v>34</v>
@@ -18836,7 +18836,7 @@
         <v>1378</v>
       </c>
       <c r="K233" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="L233" s="1" t="s">
         <v>1379</v>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>34</v>
@@ -19337,7 +19337,7 @@
         <v>1429</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M241" s="1" t="s">
         <v>1434</v>
@@ -19454,10 +19454,10 @@
         <v>1446</v>
       </c>
       <c r="K243" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M243" s="1" t="s">
         <v>1445</v>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="P243" s="1"/>
       <c r="Q243" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R243" s="1" t="s">
         <v>34</v>
@@ -19514,10 +19514,10 @@
         <v>1452</v>
       </c>
       <c r="K244" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M244" s="1" t="s">
         <v>1451</v>
@@ -19566,22 +19566,22 @@
         <v>27</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H245" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J245" s="1" t="s">
         <v>1452</v>
       </c>
       <c r="K245" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="M245" s="1" t="s">
         <v>1456</v>
@@ -19769,7 +19769,7 @@
         <v>280</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1479</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R248" s="1" t="s">
         <v>34</v>
@@ -19831,7 +19831,7 @@
         <v>280</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1479</v>
@@ -19844,7 +19844,7 @@
       </c>
       <c r="P249" s="1"/>
       <c r="Q249" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R249" s="1" t="s">
         <v>34</v>
@@ -19964,7 +19964,7 @@
       </c>
       <c r="P251" s="1"/>
       <c r="Q251" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R251" s="1" t="s">
         <v>34</v>
@@ -20375,7 +20375,7 @@
         <v>1547</v>
       </c>
       <c r="L258" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M258" s="1" t="s">
         <v>1543</v>
@@ -20388,7 +20388,7 @@
       </c>
       <c r="P258" s="1"/>
       <c r="Q258" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R258" s="1" t="s">
         <v>34</v>
@@ -20437,7 +20437,7 @@
         <v>1547</v>
       </c>
       <c r="L259" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M259" s="1" t="s">
         <v>1553</v>
@@ -20450,7 +20450,7 @@
       </c>
       <c r="P259" s="1"/>
       <c r="Q259" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R259" s="1" t="s">
         <v>34</v>
@@ -20497,7 +20497,7 @@
         <v>467</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M260" s="1" t="s">
         <v>1561</v>
@@ -20510,7 +20510,7 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R260" s="1" t="s">
         <v>34</v>
@@ -20610,13 +20610,13 @@
         <v>27</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H262" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I262" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J262" s="1" t="s">
         <v>1574</v>
@@ -20758,7 +20758,7 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R264" s="1" t="s">
         <v>34</v>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R265" s="1" t="s">
         <v>34</v>
@@ -20871,7 +20871,7 @@
         <v>737</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>1606</v>
@@ -20933,7 +20933,7 @@
         <v>737</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1606</v>
@@ -20997,7 +20997,7 @@
         <v>59</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1618</v>
@@ -21061,7 +21061,7 @@
         <v>59</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1625</v>
@@ -21112,13 +21112,13 @@
         <v>195</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H270" s="1" t="s">
         <v>1634</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J270" s="1" t="s">
         <v>1635</v>
@@ -21142,7 +21142,7 @@
         <v>1639</v>
       </c>
       <c r="Q270" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R270" s="1" t="s">
         <v>34</v>
@@ -21180,13 +21180,13 @@
         <v>195</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H271" s="1" t="s">
         <v>1634</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J271" s="1" t="s">
         <v>1635</v>
@@ -21210,7 +21210,7 @@
         <v>1639</v>
       </c>
       <c r="Q271" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R271" s="1" t="s">
         <v>34</v>
@@ -21321,7 +21321,7 @@
         <v>1345</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="M273" s="1" t="s">
         <v>1657</v>
@@ -21334,7 +21334,7 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R273" s="1" t="s">
         <v>34</v>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="P274" s="1"/>
       <c r="Q274" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>34</v>
@@ -21458,7 +21458,7 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>34</v>
@@ -21991,7 +21991,7 @@
         <v>1739</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M284" s="1" t="s">
         <v>1736</v>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="P284" s="1"/>
       <c r="Q284" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R284" s="1" t="s">
         <v>34</v>
@@ -22049,7 +22049,7 @@
         <v>1744</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M285" s="1" t="s">
         <v>1736</v>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="P285" s="1"/>
       <c r="Q285" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="R285" s="1" t="s">
         <v>34</v>
